--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:04:23+00:00</t>
+    <t>2026-10-15T15:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$104</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4210" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4295" uniqueCount="775">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:21:59+00:00</t>
+    <t>2026-10-15T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1247,7 +1247,11 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J08-XdsConfidentialityCode-CISIS/FHIR/JDV-J08-XdsConfidentialityCode-CISIS</t>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>niveauConfidentialite : [0..*] code</t>
@@ -1266,6 +1270,30 @@
   </si>
   <si>
     <t>TXA-18</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:confidentiality</t>
+  </si>
+  <si>
+    <t>confidentiality</t>
+  </si>
+  <si>
+    <t>Niveau de confidentialité standard du document (Normal, Restreint, Très restreint, ...). En l'absence d'information de confidentialité disponible, la valeur par défaut à utiliser est N (Normal), conformément à ce qui est déjà pratiqué aujourd'hui pour les documents CDA. L'ensemble des codes est autorisé pour permettre un usage large de PDSm.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-Confidentiality</t>
+  </si>
+  <si>
+    <t>DocumentReference.securityLabel:visibilityStatus</t>
+  </si>
+  <si>
+    <t>visibilityStatus</t>
+  </si>
+  <si>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -2721,7 +2749,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS102"/>
+  <dimension ref="A1:AS104"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.97265625" customWidth="true" bestFit="true"/>
@@ -2752,7 +2780,7 @@
     <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="37.625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="255.0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -7660,7 +7688,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>387</v>
       </c>
@@ -7727,24 +7755,26 @@
       <c r="X39" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="Z39" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AC39" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>387</v>
@@ -7762,41 +7792,43 @@
         <v>109</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AS39" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>394</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7817,16 +7849,20 @@
         <v>98</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>259</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7850,13 +7886,11 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7874,10 +7908,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>84</v>
@@ -7892,38 +7926,40 @@
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7932,28 +7968,32 @@
         <v>83</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>112</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7977,13 +8017,11 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -8001,87 +8039,85 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>114</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>115</v>
+        <v>397</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AS41" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>118</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>119</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -8130,10 +8166,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>125</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>84</v>
@@ -8142,7 +8178,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -8154,10 +8190,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8174,46 +8210,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -8261,19 +8293,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -8288,7 +8320,7 @@
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -8305,21 +8337,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -8328,18 +8360,20 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>408</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>409</v>
+        <v>119</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -8388,19 +8422,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>125</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -8412,22 +8446,22 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>403</v>
+        <v>115</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -8439,35 +8473,39 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -8515,19 +8553,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>114</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -8542,7 +8580,7 @@
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -8566,14 +8604,14 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -8582,20 +8620,18 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>118</v>
+        <v>417</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>119</v>
+        <v>418</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8632,31 +8668,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>125</v>
+        <v>416</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8668,30 +8704,30 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8699,7 +8735,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>97</v>
@@ -8711,21 +8747,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
+        <v>113</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>420</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -8737,7 +8771,7 @@
         <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>82</v>
@@ -8749,13 +8783,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8773,7 +8807,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>114</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8785,76 +8819,76 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>119</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8866,7 +8900,7 @@
         <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>82</v>
@@ -8878,49 +8912,49 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>125</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
@@ -8929,7 +8963,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>436</v>
+        <v>115</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8946,10 +8980,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8957,10 +8991,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8969,22 +9003,20 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>438</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8997,7 +9029,7 @@
         <v>82</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>82</v>
@@ -9009,13 +9041,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -9033,7 +9065,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9051,7 +9083,7 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
@@ -9060,7 +9092,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -9069,18 +9101,18 @@
         <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9094,7 +9126,7 @@
         <v>97</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -9103,19 +9135,17 @@
         <v>98</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>447</v>
+        <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9128,7 +9158,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9140,13 +9170,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -9164,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9176,13 +9206,13 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>454</v>
+        <v>109</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -9191,7 +9221,7 @@
         <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -9200,7 +9230,7 @@
         <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AS50" t="s" s="2">
         <v>82</v>
@@ -9208,10 +9238,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9219,10 +9249,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -9231,22 +9261,22 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9295,7 +9325,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9313,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
@@ -9322,7 +9352,7 @@
         <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9331,7 +9361,7 @@
         <v>82</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
       <c r="AS51" t="s" s="2">
         <v>82</v>
@@ -9339,10 +9369,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9365,19 +9395,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9390,7 +9420,7 @@
         <v>82</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>82</v>
@@ -9426,7 +9456,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9438,13 +9468,13 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>109</v>
+        <v>463</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
@@ -9453,7 +9483,7 @@
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -9462,7 +9492,7 @@
         <v>82</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AS52" t="s" s="2">
         <v>82</v>
@@ -9470,10 +9500,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9496,17 +9526,19 @@
         <v>98</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>111</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9519,7 +9551,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>480</v>
+        <v>82</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -9555,7 +9587,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9570,10 +9602,10 @@
         <v>109</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
@@ -9582,7 +9614,7 @@
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9597,12 +9629,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9616,7 +9648,7 @@
         <v>97</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -9625,17 +9657,19 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9684,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9699,10 +9733,10 @@
         <v>109</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
@@ -9711,7 +9745,7 @@
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9726,12 +9760,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9745,7 +9779,7 @@
         <v>97</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9754,18 +9788,18 @@
         <v>98</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9777,7 +9811,7 @@
         <v>82</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>82</v>
@@ -9789,11 +9823,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -9811,37 +9847,37 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AG55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="AP55" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>82</v>
@@ -9850,15 +9886,15 @@
         <v>82</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9881,18 +9917,18 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>341</v>
+        <v>495</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9940,7 +9976,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9955,10 +9991,10 @@
         <v>109</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
@@ -9967,7 +10003,7 @@
         <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9982,12 +10018,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9995,30 +10031,32 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>112</v>
+        <v>503</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -10043,13 +10081,11 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -10067,7 +10103,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>114</v>
+        <v>502</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -10079,25 +10115,25 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>508</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>115</v>
+        <v>412</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>82</v>
@@ -10106,47 +10142,47 @@
         <v>82</v>
       </c>
       <c r="AS57" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>118</v>
+        <v>341</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>119</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>120</v>
+        <v>514</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>121</v>
+        <v>515</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10196,19 +10232,19 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>125</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -10223,7 +10259,7 @@
         <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>115</v>
+        <v>516</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10240,46 +10276,42 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -10327,19 +10359,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>356</v>
+        <v>114</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -10354,7 +10386,7 @@
         <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -10371,14 +10403,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10397,15 +10429,17 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>512</v>
+        <v>118</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>513</v>
+        <v>119</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -10454,7 +10488,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>511</v>
+        <v>125</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10466,28 +10500,28 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>518</v>
+        <v>115</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>82</v>
@@ -10498,14 +10532,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10518,24 +10552,26 @@
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>521</v>
+        <v>353</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>522</v>
+        <v>354</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -10559,13 +10595,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -10583,7 +10619,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>356</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10595,22 +10631,22 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>526</v>
+        <v>126</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>530</v>
+        <v>198</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -10622,15 +10658,15 @@
         <v>82</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>528</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10638,28 +10674,28 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10710,13 +10746,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10728,36 +10764,36 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10768,7 +10804,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -10780,15 +10816,17 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>112</v>
+        <v>530</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10813,13 +10851,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10837,34 +10875,34 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>114</v>
+        <v>529</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>115</v>
+        <v>539</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -10876,10 +10914,10 @@
         <v>82</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>540</v>
       </c>
@@ -10888,36 +10926,34 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>118</v>
+        <v>541</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>119</v>
+        <v>542</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10954,31 +10990,31 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>125</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -10990,13 +11026,13 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>115</v>
+        <v>545</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>82</v>
@@ -11005,15 +11041,15 @@
         <v>82</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11021,7 +11057,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>97</v>
@@ -11033,20 +11069,18 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>486</v>
+        <v>111</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>542</v>
+        <v>112</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -11095,7 +11129,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -11104,16 +11138,16 @@
         <v>97</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
@@ -11122,7 +11156,7 @@
         <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>549</v>
+        <v>115</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -11131,7 +11165,7 @@
         <v>82</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AS65" t="s" s="2">
         <v>82</v>
@@ -11139,21 +11173,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -11162,27 +11196,25 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>486</v>
+        <v>118</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>119</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>553</v>
+        <v>120</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>554</v>
+        <v>121</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q66" t="s" s="2">
-        <v>555</v>
-      </c>
+      <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
         <v>82</v>
       </c>
@@ -11214,37 +11246,37 @@
         <v>82</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>556</v>
+        <v>125</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
@@ -11253,7 +11285,7 @@
         <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>559</v>
+        <v>115</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
@@ -11262,18 +11294,18 @@
         <v>82</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="AS66" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11287,24 +11319,26 @@
         <v>97</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -11329,11 +11363,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -11351,7 +11387,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11360,45 +11396,45 @@
         <v>97</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>565</v>
+        <v>109</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AS67" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11406,39 +11442,39 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>259</v>
+        <v>495</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>82</v>
       </c>
@@ -11458,11 +11494,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -11480,7 +11518,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11489,45 +11527,45 @@
         <v>97</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>565</v>
+        <v>109</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AO68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AP68" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AS68" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11550,13 +11588,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>580</v>
+        <v>259</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11583,13 +11621,11 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -11607,38 +11643,38 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
       </c>
@@ -11646,15 +11682,15 @@
         <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11662,13 +11698,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
@@ -11677,16 +11713,20 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>112</v>
+        <v>581</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -11710,13 +11750,11 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11734,7 +11772,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>114</v>
+        <v>580</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11746,25 +11784,25 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>115</v>
+        <v>578</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>82</v>
@@ -11773,29 +11811,29 @@
         <v>82</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>82</v>
@@ -11804,17 +11842,15 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>118</v>
+        <v>589</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>119</v>
+        <v>590</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>121</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11851,31 +11887,31 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>125</v>
+        <v>588</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11887,13 +11923,13 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>82</v>
@@ -11902,15 +11938,15 @@
         <v>82</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11930,20 +11966,18 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>587</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11992,7 +12026,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>590</v>
+        <v>114</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12001,16 +12035,16 @@
         <v>97</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>592</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
@@ -12019,7 +12053,7 @@
         <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
@@ -12036,21 +12070,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -12059,19 +12093,19 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>594</v>
+        <v>119</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12097,43 +12131,43 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>599</v>
+        <v>125</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -12148,7 +12182,7 @@
         <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
@@ -12165,10 +12199,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12191,16 +12225,16 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12250,7 +12284,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12259,7 +12293,7 @@
         <v>97</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>109</v>
@@ -12268,7 +12302,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
@@ -12277,7 +12311,7 @@
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>606</v>
+        <v>198</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>82</v>
@@ -12294,10 +12328,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12320,16 +12354,16 @@
         <v>98</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12355,13 +12389,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -12379,7 +12413,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12423,10 +12457,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12437,28 +12471,28 @@
         <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="I76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K76" t="s" s="2">
-        <v>613</v>
+        <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12496,25 +12530,25 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -12526,19 +12560,19 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>82</v>
@@ -12547,19 +12581,17 @@
         <v>82</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -12568,7 +12600,7 @@
         <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -12577,19 +12609,19 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>613</v>
+        <v>111</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12639,13 +12671,13 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
@@ -12657,19 +12689,19 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>621</v>
+        <v>198</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>82</v>
@@ -12678,15 +12710,15 @@
         <v>82</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12697,10 +12729,10 @@
         <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>82</v>
@@ -12709,15 +12741,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>111</v>
+        <v>622</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>623</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -12754,49 +12788,49 @@
         <v>82</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>82</v>
+        <v>626</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>114</v>
+        <v>621</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>115</v>
+        <v>630</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>82</v>
@@ -12805,19 +12839,21 @@
         <v>82</v>
       </c>
       <c r="AS78" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12836,16 +12872,16 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>118</v>
+        <v>622</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>119</v>
+        <v>635</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>120</v>
+        <v>624</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>121</v>
+        <v>625</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12883,19 +12919,19 @@
         <v>82</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>125</v>
+        <v>621</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12907,25 +12943,25 @@
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>115</v>
+        <v>630</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>82</v>
@@ -12934,15 +12970,15 @@
         <v>82</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>82</v>
+        <v>632</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12962,20 +12998,18 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>587</v>
+        <v>112</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -13024,7 +13058,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>590</v>
+        <v>114</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13033,10 +13067,10 @@
         <v>97</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -13051,7 +13085,7 @@
         <v>82</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>82</v>
@@ -13068,21 +13102,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -13091,19 +13125,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>594</v>
+        <v>119</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>595</v>
+        <v>120</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>596</v>
+        <v>121</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13129,43 +13163,43 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>597</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>599</v>
+        <v>125</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -13180,7 +13214,7 @@
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
@@ -13195,12 +13229,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13214,7 +13248,7 @@
         <v>97</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -13223,16 +13257,16 @@
         <v>98</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>227</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13282,7 +13316,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13291,7 +13325,7 @@
         <v>97</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>109</v>
@@ -13309,7 +13343,7 @@
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>606</v>
+        <v>198</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -13326,10 +13360,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13349,18 +13383,20 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>112</v>
+        <v>603</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -13385,13 +13421,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -13409,7 +13445,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>114</v>
+        <v>608</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13421,7 +13457,7 @@
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -13436,7 +13472,7 @@
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>82</v>
@@ -13451,44 +13487,44 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>118</v>
+        <v>227</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>119</v>
+        <v>610</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>120</v>
+        <v>611</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>121</v>
+        <v>612</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13526,31 +13562,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>125</v>
+        <v>613</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -13565,7 +13601,7 @@
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>115</v>
+        <v>615</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13582,10 +13618,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13602,26 +13638,22 @@
         <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>643</v>
+        <v>112</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -13645,13 +13677,13 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>648</v>
+        <v>82</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>82</v>
@@ -13669,7 +13701,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>649</v>
+        <v>114</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13681,7 +13713,7 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -13696,7 +13728,7 @@
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>650</v>
+        <v>115</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
@@ -13705,7 +13737,7 @@
         <v>82</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AS85" t="s" s="2">
         <v>82</v>
@@ -13713,21 +13745,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -13736,23 +13768,21 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>653</v>
+        <v>119</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>654</v>
+        <v>120</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>656</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -13776,43 +13806,43 @@
         <v>82</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>657</v>
+        <v>82</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>659</v>
+        <v>125</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -13827,7 +13857,7 @@
         <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>650</v>
+        <v>115</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>82</v>
@@ -13836,7 +13866,7 @@
         <v>82</v>
       </c>
       <c r="AR86" t="s" s="2">
-        <v>660</v>
+        <v>82</v>
       </c>
       <c r="AS86" t="s" s="2">
         <v>82</v>
@@ -13844,10 +13874,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13864,22 +13894,26 @@
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>652</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>655</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13903,13 +13937,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>656</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -13927,7 +13961,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>114</v>
+        <v>658</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13939,7 +13973,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13954,7 +13988,7 @@
         <v>82</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>115</v>
+        <v>659</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -13963,7 +13997,7 @@
         <v>82</v>
       </c>
       <c r="AR87" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="AS87" t="s" s="2">
         <v>82</v>
@@ -13971,21 +14005,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13994,21 +14028,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>119</v>
+        <v>662</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>120</v>
+        <v>663</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>664</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -14032,43 +14068,43 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>82</v>
+        <v>666</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>667</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>125</v>
+        <v>668</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -14083,7 +14119,7 @@
         <v>82</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>115</v>
+        <v>659</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14092,7 +14128,7 @@
         <v>82</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AS88" t="s" s="2">
         <v>82</v>
@@ -14100,10 +14136,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14114,7 +14150,7 @@
         <v>83</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -14123,23 +14159,19 @@
         <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>667</v>
+        <v>112</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>670</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -14187,19 +14219,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>671</v>
+        <v>114</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -14214,7 +14246,7 @@
         <v>82</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>672</v>
+        <v>115</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>82</v>
@@ -14223,7 +14255,7 @@
         <v>82</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>673</v>
+        <v>82</v>
       </c>
       <c r="AS89" t="s" s="2">
         <v>82</v>
@@ -14231,21 +14263,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -14257,15 +14289,17 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>121</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -14302,31 +14336,31 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -14358,14 +14392,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -14381,21 +14415,23 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>119</v>
+        <v>676</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>120</v>
+        <v>677</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -14431,19 +14467,19 @@
         <v>82</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>125</v>
+        <v>680</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14455,7 +14491,7 @@
         <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -14470,7 +14506,7 @@
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>115</v>
+        <v>681</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>82</v>
@@ -14479,7 +14515,7 @@
         <v>82</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="AS91" t="s" s="2">
         <v>82</v>
@@ -14487,10 +14523,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14510,23 +14546,19 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>680</v>
+        <v>112</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -14535,7 +14567,7 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>82</v>
@@ -14574,7 +14606,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>685</v>
+        <v>114</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14586,7 +14618,7 @@
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
@@ -14601,7 +14633,7 @@
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>686</v>
+        <v>115</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
@@ -14610,7 +14642,7 @@
         <v>82</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>687</v>
+        <v>82</v>
       </c>
       <c r="AS92" t="s" s="2">
         <v>82</v>
@@ -14618,21 +14650,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -14641,19 +14673,19 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>690</v>
+        <v>119</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>691</v>
+        <v>120</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>692</v>
+        <v>121</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14691,31 +14723,31 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>693</v>
+        <v>125</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -14730,7 +14762,7 @@
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>694</v>
+        <v>115</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>82</v>
@@ -14739,18 +14771,18 @@
         <v>82</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>695</v>
+        <v>82</v>
       </c>
       <c r="AS93" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14764,7 +14796,7 @@
         <v>97</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>82</v>
@@ -14773,17 +14805,19 @@
         <v>98</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>691</v>
+      </c>
       <c r="O94" t="s" s="2">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -14793,7 +14827,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>82</v>
+        <v>693</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -14832,7 +14866,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14859,7 +14893,7 @@
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>269</v>
+        <v>695</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
@@ -14868,7 +14902,7 @@
         <v>82</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14876,10 +14910,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14905,15 +14939,15 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>707</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -14961,7 +14995,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -14988,7 +15022,7 @@
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
@@ -14997,18 +15031,18 @@
         <v>82</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15022,7 +15056,7 @@
         <v>97</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -15031,19 +15065,17 @@
         <v>98</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>713</v>
+        <v>175</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>716</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -15092,7 +15124,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -15119,7 +15151,7 @@
         <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>719</v>
+        <v>269</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
@@ -15128,7 +15160,7 @@
         <v>82</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15136,10 +15168,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15165,16 +15197,14 @@
         <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -15223,7 +15253,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15250,7 +15280,7 @@
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
@@ -15259,18 +15289,18 @@
         <v>82</v>
       </c>
       <c r="AR97" t="s" s="2">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15284,7 +15314,7 @@
         <v>97</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
@@ -15293,19 +15323,19 @@
         <v>98</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>140</v>
+        <v>722</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
@@ -15318,7 +15348,7 @@
         <v>82</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>736</v>
+        <v>82</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>82</v>
@@ -15354,7 +15384,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15381,7 +15411,7 @@
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -15390,18 +15420,18 @@
         <v>82</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15409,13 +15439,13 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>82</v>
@@ -15427,15 +15457,17 @@
         <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>734</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>735</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -15447,7 +15479,7 @@
         <v>82</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>745</v>
+        <v>82</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>82</v>
@@ -15483,7 +15515,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -15510,7 +15542,7 @@
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
@@ -15519,18 +15551,18 @@
         <v>82</v>
       </c>
       <c r="AR99" t="s" s="2">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15544,7 +15576,7 @@
         <v>97</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -15553,16 +15585,20 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>532</v>
+        <v>140</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>742</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>744</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -15574,7 +15610,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>82</v>
+        <v>745</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -15610,7 +15646,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>83</v>
@@ -15637,7 +15673,7 @@
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
@@ -15646,18 +15682,18 @@
         <v>82</v>
       </c>
       <c r="AR100" t="s" s="2">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15665,13 +15701,13 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>97</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>82</v>
@@ -15680,16 +15716,16 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15703,7 +15739,7 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>82</v>
+        <v>754</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>82</v>
@@ -15739,7 +15775,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15766,7 +15802,7 @@
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -15775,7 +15811,7 @@
         <v>82</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15783,10 +15819,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15809,17 +15845,15 @@
         <v>98</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>541</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>608</v>
+        <v>760</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -15868,7 +15902,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>611</v>
+        <v>762</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15895,23 +15929,281 @@
         <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR102" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AS102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR103" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AS103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AP102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS102" t="s" s="2">
+      <c r="AP104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS104" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS102">
+  <autoFilter ref="A1:AS104">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15921,7 +16213,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI101">
+  <conditionalFormatting sqref="A2:AI103">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
